--- a/Compititor's_Price/Unilin_Prices/Unilin_Prices_06-08-2025.xlsx
+++ b/Compititor's_Price/Unilin_Prices/Unilin_Prices_06-08-2025.xlsx
@@ -595,29 +595,29 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
+          <t>£12.33</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>£12.33</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>£12.33</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>N/L</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
           <t>£12.62</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>£12.62</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>£12.62</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>N/L</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>£12.62</t>
-        </is>
-      </c>
       <c r="H3" t="inlineStr">
         <is>
           <t>N/L</t>
@@ -636,27 +636,27 @@
       <c r="K3" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=138.0.7204.184); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+  (Session info: chrome=139.0.7258.67); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff6f54ae415+77285]
-	GetHandleVerifier [0x0x7ff6f54ae470+77376]
-	(No symbol) [0x0x7ff6f5279a6a]
-	(No symbol) [0x0x7ff6f52d0406]
-	(No symbol) [0x0x7ff6f52d06bc]
-	(No symbol) [0x0x7ff6f5323ac7]
-	(No symbol) [0x0x7ff6f52f864f]
-	(No symbol) [0x0x7ff6f532087f]
-	(No symbol) [0x0x7ff6f52f83e3]
-	(No symbol) [0x0x7ff6f52c1521]
-	(No symbol) [0x0x7ff6f52c22b3]
-	GetHandleVerifier [0x0x7ff6f5791efd+3107021]
-	GetHandleVerifier [0x0x7ff6f578c29d+3083373]
-	GetHandleVerifier [0x0x7ff6f57abedd+3213485]
-	GetHandleVerifier [0x0x7ff6f54c884e+184862]
-	GetHandleVerifier [0x0x7ff6f54d055f+216879]
-	GetHandleVerifier [0x0x7ff6f54b7084+113236]
-	GetHandleVerifier [0x0x7ff6f54b7239+113673]
-	GetHandleVerifier [0x0x7ff6f549e298+11368]
+	GetHandleVerifier [0x0x7ff6fc6a6b55+79621]
+	GetHandleVerifier [0x0x7ff6fc6a6bb0+79712]
+	(No symbol) [0x0x7ff6fc43c0ea]
+	(No symbol) [0x0x7ff6fc492f56]
+	(No symbol) [0x0x7ff6fc49320c]
+	(No symbol) [0x0x7ff6fc4e65b7]
+	(No symbol) [0x0x7ff6fc4bb17f]
+	(No symbol) [0x0x7ff6fc4e33d0]
+	(No symbol) [0x0x7ff6fc4baf13]
+	(No symbol) [0x0x7ff6fc484151]
+	(No symbol) [0x0x7ff6fc484ee3]
+	GetHandleVerifier [0x0x7ff6fc96686d+2962461]
+	GetHandleVerifier [0x0x7ff6fc960b8d+2938685]
+	GetHandleVerifier [0x0x7ff6fc97f74d+3064573]
+	GetHandleVerifier [0x0x7ff6fc6c0c9e+186446]
+	GetHandleVerifier [0x0x7ff6fc6c8a6f+218655]
+	GetHandleVerifier [0x0x7ff6fc6af944+115956]
+	GetHandleVerifier [0x0x7ff6fc6afaf9+116393]
+	GetHandleVerifier [0x0x7ff6fc695f28+10968]
 	BaseThreadInitThunk [0x0x7ffde661e8d7+23]
 	RtlUserThreadStart [0x0x7ffde699c34c+44]
 </t>
@@ -696,17 +696,17 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>£16.18</t>
+          <t>£15.75</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>£16.18</t>
+          <t>£15.75</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>£16.18</t>
+          <t>£15.75</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -737,27 +737,27 @@
       <c r="K4" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=138.0.7204.184); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+  (Session info: chrome=139.0.7258.67); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff6f54ae415+77285]
-	GetHandleVerifier [0x0x7ff6f54ae470+77376]
-	(No symbol) [0x0x7ff6f5279a6a]
-	(No symbol) [0x0x7ff6f52d0406]
-	(No symbol) [0x0x7ff6f52d06bc]
-	(No symbol) [0x0x7ff6f5323ac7]
-	(No symbol) [0x0x7ff6f52f864f]
-	(No symbol) [0x0x7ff6f532087f]
-	(No symbol) [0x0x7ff6f52f83e3]
-	(No symbol) [0x0x7ff6f52c1521]
-	(No symbol) [0x0x7ff6f52c22b3]
-	GetHandleVerifier [0x0x7ff6f5791efd+3107021]
-	GetHandleVerifier [0x0x7ff6f578c29d+3083373]
-	GetHandleVerifier [0x0x7ff6f57abedd+3213485]
-	GetHandleVerifier [0x0x7ff6f54c884e+184862]
-	GetHandleVerifier [0x0x7ff6f54d055f+216879]
-	GetHandleVerifier [0x0x7ff6f54b7084+113236]
-	GetHandleVerifier [0x0x7ff6f54b7239+113673]
-	GetHandleVerifier [0x0x7ff6f549e298+11368]
+	GetHandleVerifier [0x0x7ff6fc6a6b55+79621]
+	GetHandleVerifier [0x0x7ff6fc6a6bb0+79712]
+	(No symbol) [0x0x7ff6fc43c0ea]
+	(No symbol) [0x0x7ff6fc492f56]
+	(No symbol) [0x0x7ff6fc49320c]
+	(No symbol) [0x0x7ff6fc4e65b7]
+	(No symbol) [0x0x7ff6fc4bb17f]
+	(No symbol) [0x0x7ff6fc4e33d0]
+	(No symbol) [0x0x7ff6fc4baf13]
+	(No symbol) [0x0x7ff6fc484151]
+	(No symbol) [0x0x7ff6fc484ee3]
+	GetHandleVerifier [0x0x7ff6fc96686d+2962461]
+	GetHandleVerifier [0x0x7ff6fc960b8d+2938685]
+	GetHandleVerifier [0x0x7ff6fc97f74d+3064573]
+	GetHandleVerifier [0x0x7ff6fc6c0c9e+186446]
+	GetHandleVerifier [0x0x7ff6fc6c8a6f+218655]
+	GetHandleVerifier [0x0x7ff6fc6af944+115956]
+	GetHandleVerifier [0x0x7ff6fc6afaf9+116393]
+	GetHandleVerifier [0x0x7ff6fc695f28+10968]
 	BaseThreadInitThunk [0x0x7ffde661e8d7+23]
 	RtlUserThreadStart [0x0x7ffde699c34c+44]
 </t>
@@ -797,29 +797,29 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
+          <t>£16.50</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>£16.50</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>£16.50</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>POA or OOS</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
           <t>£16.60</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>£16.60</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>£16.60</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>POA or OOS</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>£16.60</t>
-        </is>
-      </c>
       <c r="H5" t="inlineStr">
         <is>
           <t>N/L</t>
@@ -838,27 +838,27 @@
       <c r="K5" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=138.0.7204.184); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+  (Session info: chrome=139.0.7258.67); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff6f54ae415+77285]
-	GetHandleVerifier [0x0x7ff6f54ae470+77376]
-	(No symbol) [0x0x7ff6f5279a6a]
-	(No symbol) [0x0x7ff6f52d0406]
-	(No symbol) [0x0x7ff6f52d06bc]
-	(No symbol) [0x0x7ff6f5323ac7]
-	(No symbol) [0x0x7ff6f52f864f]
-	(No symbol) [0x0x7ff6f532087f]
-	(No symbol) [0x0x7ff6f52f83e3]
-	(No symbol) [0x0x7ff6f52c1521]
-	(No symbol) [0x0x7ff6f52c22b3]
-	GetHandleVerifier [0x0x7ff6f5791efd+3107021]
-	GetHandleVerifier [0x0x7ff6f578c29d+3083373]
-	GetHandleVerifier [0x0x7ff6f57abedd+3213485]
-	GetHandleVerifier [0x0x7ff6f54c884e+184862]
-	GetHandleVerifier [0x0x7ff6f54d055f+216879]
-	GetHandleVerifier [0x0x7ff6f54b7084+113236]
-	GetHandleVerifier [0x0x7ff6f54b7239+113673]
-	GetHandleVerifier [0x0x7ff6f549e298+11368]
+	GetHandleVerifier [0x0x7ff6fc6a6b55+79621]
+	GetHandleVerifier [0x0x7ff6fc6a6bb0+79712]
+	(No symbol) [0x0x7ff6fc43c0ea]
+	(No symbol) [0x0x7ff6fc492f56]
+	(No symbol) [0x0x7ff6fc49320c]
+	(No symbol) [0x0x7ff6fc4e65b7]
+	(No symbol) [0x0x7ff6fc4bb17f]
+	(No symbol) [0x0x7ff6fc4e33d0]
+	(No symbol) [0x0x7ff6fc4baf13]
+	(No symbol) [0x0x7ff6fc484151]
+	(No symbol) [0x0x7ff6fc484ee3]
+	GetHandleVerifier [0x0x7ff6fc96686d+2962461]
+	GetHandleVerifier [0x0x7ff6fc960b8d+2938685]
+	GetHandleVerifier [0x0x7ff6fc97f74d+3064573]
+	GetHandleVerifier [0x0x7ff6fc6c0c9e+186446]
+	GetHandleVerifier [0x0x7ff6fc6c8a6f+218655]
+	GetHandleVerifier [0x0x7ff6fc6af944+115956]
+	GetHandleVerifier [0x0x7ff6fc6afaf9+116393]
+	GetHandleVerifier [0x0x7ff6fc695f28+10968]
 	BaseThreadInitThunk [0x0x7ffde661e8d7+23]
 	RtlUserThreadStart [0x0x7ffde699c34c+44]
 </t>
@@ -903,12 +903,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>£21.08</t>
+          <t>£21.00</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>£21.08</t>
+          <t>£21.00</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -939,27 +939,27 @@
       <c r="K6" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=138.0.7204.184); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+  (Session info: chrome=139.0.7258.67); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff6f54ae415+77285]
-	GetHandleVerifier [0x0x7ff6f54ae470+77376]
-	(No symbol) [0x0x7ff6f5279a6a]
-	(No symbol) [0x0x7ff6f52d0406]
-	(No symbol) [0x0x7ff6f52d06bc]
-	(No symbol) [0x0x7ff6f5323ac7]
-	(No symbol) [0x0x7ff6f52f864f]
-	(No symbol) [0x0x7ff6f532087f]
-	(No symbol) [0x0x7ff6f52f83e3]
-	(No symbol) [0x0x7ff6f52c1521]
-	(No symbol) [0x0x7ff6f52c22b3]
-	GetHandleVerifier [0x0x7ff6f5791efd+3107021]
-	GetHandleVerifier [0x0x7ff6f578c29d+3083373]
-	GetHandleVerifier [0x0x7ff6f57abedd+3213485]
-	GetHandleVerifier [0x0x7ff6f54c884e+184862]
-	GetHandleVerifier [0x0x7ff6f54d055f+216879]
-	GetHandleVerifier [0x0x7ff6f54b7084+113236]
-	GetHandleVerifier [0x0x7ff6f54b7239+113673]
-	GetHandleVerifier [0x0x7ff6f549e298+11368]
+	GetHandleVerifier [0x0x7ff6fc6a6b55+79621]
+	GetHandleVerifier [0x0x7ff6fc6a6bb0+79712]
+	(No symbol) [0x0x7ff6fc43c0ea]
+	(No symbol) [0x0x7ff6fc492f56]
+	(No symbol) [0x0x7ff6fc49320c]
+	(No symbol) [0x0x7ff6fc4e65b7]
+	(No symbol) [0x0x7ff6fc4bb17f]
+	(No symbol) [0x0x7ff6fc4e33d0]
+	(No symbol) [0x0x7ff6fc4baf13]
+	(No symbol) [0x0x7ff6fc484151]
+	(No symbol) [0x0x7ff6fc484ee3]
+	GetHandleVerifier [0x0x7ff6fc96686d+2962461]
+	GetHandleVerifier [0x0x7ff6fc960b8d+2938685]
+	GetHandleVerifier [0x0x7ff6fc97f74d+3064573]
+	GetHandleVerifier [0x0x7ff6fc6c0c9e+186446]
+	GetHandleVerifier [0x0x7ff6fc6c8a6f+218655]
+	GetHandleVerifier [0x0x7ff6fc6af944+115956]
+	GetHandleVerifier [0x0x7ff6fc6afaf9+116393]
+	GetHandleVerifier [0x0x7ff6fc695f28+10968]
 	BaseThreadInitThunk [0x0x7ffde661e8d7+23]
 	RtlUserThreadStart [0x0x7ffde699c34c+44]
 </t>
@@ -1040,27 +1040,27 @@
       <c r="K7" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=138.0.7204.184); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+  (Session info: chrome=139.0.7258.67); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff6f54ae415+77285]
-	GetHandleVerifier [0x0x7ff6f54ae470+77376]
-	(No symbol) [0x0x7ff6f5279a6a]
-	(No symbol) [0x0x7ff6f52d0406]
-	(No symbol) [0x0x7ff6f52d06bc]
-	(No symbol) [0x0x7ff6f5323ac7]
-	(No symbol) [0x0x7ff6f52f864f]
-	(No symbol) [0x0x7ff6f532087f]
-	(No symbol) [0x0x7ff6f52f83e3]
-	(No symbol) [0x0x7ff6f52c1521]
-	(No symbol) [0x0x7ff6f52c22b3]
-	GetHandleVerifier [0x0x7ff6f5791efd+3107021]
-	GetHandleVerifier [0x0x7ff6f578c29d+3083373]
-	GetHandleVerifier [0x0x7ff6f57abedd+3213485]
-	GetHandleVerifier [0x0x7ff6f54c884e+184862]
-	GetHandleVerifier [0x0x7ff6f54d055f+216879]
-	GetHandleVerifier [0x0x7ff6f54b7084+113236]
-	GetHandleVerifier [0x0x7ff6f54b7239+113673]
-	GetHandleVerifier [0x0x7ff6f549e298+11368]
+	GetHandleVerifier [0x0x7ff6fc6a6b55+79621]
+	GetHandleVerifier [0x0x7ff6fc6a6bb0+79712]
+	(No symbol) [0x0x7ff6fc43c0ea]
+	(No symbol) [0x0x7ff6fc492f56]
+	(No symbol) [0x0x7ff6fc49320c]
+	(No symbol) [0x0x7ff6fc4e65b7]
+	(No symbol) [0x0x7ff6fc4bb17f]
+	(No symbol) [0x0x7ff6fc4e33d0]
+	(No symbol) [0x0x7ff6fc4baf13]
+	(No symbol) [0x0x7ff6fc484151]
+	(No symbol) [0x0x7ff6fc484ee3]
+	GetHandleVerifier [0x0x7ff6fc96686d+2962461]
+	GetHandleVerifier [0x0x7ff6fc960b8d+2938685]
+	GetHandleVerifier [0x0x7ff6fc97f74d+3064573]
+	GetHandleVerifier [0x0x7ff6fc6c0c9e+186446]
+	GetHandleVerifier [0x0x7ff6fc6c8a6f+218655]
+	GetHandleVerifier [0x0x7ff6fc6af944+115956]
+	GetHandleVerifier [0x0x7ff6fc6afaf9+116393]
+	GetHandleVerifier [0x0x7ff6fc695f28+10968]
 	BaseThreadInitThunk [0x0x7ffde661e8d7+23]
 	RtlUserThreadStart [0x0x7ffde699c34c+44]
 </t>
@@ -1141,27 +1141,27 @@
       <c r="K8" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=138.0.7204.184); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+  (Session info: chrome=139.0.7258.67); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff6f54ae415+77285]
-	GetHandleVerifier [0x0x7ff6f54ae470+77376]
-	(No symbol) [0x0x7ff6f5279a6a]
-	(No symbol) [0x0x7ff6f52d0406]
-	(No symbol) [0x0x7ff6f52d06bc]
-	(No symbol) [0x0x7ff6f5323ac7]
-	(No symbol) [0x0x7ff6f52f864f]
-	(No symbol) [0x0x7ff6f532087f]
-	(No symbol) [0x0x7ff6f52f83e3]
-	(No symbol) [0x0x7ff6f52c1521]
-	(No symbol) [0x0x7ff6f52c22b3]
-	GetHandleVerifier [0x0x7ff6f5791efd+3107021]
-	GetHandleVerifier [0x0x7ff6f578c29d+3083373]
-	GetHandleVerifier [0x0x7ff6f57abedd+3213485]
-	GetHandleVerifier [0x0x7ff6f54c884e+184862]
-	GetHandleVerifier [0x0x7ff6f54d055f+216879]
-	GetHandleVerifier [0x0x7ff6f54b7084+113236]
-	GetHandleVerifier [0x0x7ff6f54b7239+113673]
-	GetHandleVerifier [0x0x7ff6f549e298+11368]
+	GetHandleVerifier [0x0x7ff6fc6a6b55+79621]
+	GetHandleVerifier [0x0x7ff6fc6a6bb0+79712]
+	(No symbol) [0x0x7ff6fc43c0ea]
+	(No symbol) [0x0x7ff6fc492f56]
+	(No symbol) [0x0x7ff6fc49320c]
+	(No symbol) [0x0x7ff6fc4e65b7]
+	(No symbol) [0x0x7ff6fc4bb17f]
+	(No symbol) [0x0x7ff6fc4e33d0]
+	(No symbol) [0x0x7ff6fc4baf13]
+	(No symbol) [0x0x7ff6fc484151]
+	(No symbol) [0x0x7ff6fc484ee3]
+	GetHandleVerifier [0x0x7ff6fc96686d+2962461]
+	GetHandleVerifier [0x0x7ff6fc960b8d+2938685]
+	GetHandleVerifier [0x0x7ff6fc97f74d+3064573]
+	GetHandleVerifier [0x0x7ff6fc6c0c9e+186446]
+	GetHandleVerifier [0x0x7ff6fc6c8a6f+218655]
+	GetHandleVerifier [0x0x7ff6fc6af944+115956]
+	GetHandleVerifier [0x0x7ff6fc6afaf9+116393]
+	GetHandleVerifier [0x0x7ff6fc695f28+10968]
 	BaseThreadInitThunk [0x0x7ffde661e8d7+23]
 	RtlUserThreadStart [0x0x7ffde699c34c+44]
 </t>
@@ -1201,17 +1201,17 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>£26.50</t>
+          <t>£26.40</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>£26.50</t>
+          <t>£26.40</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>£26.50</t>
+          <t>£26.40</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -1242,27 +1242,27 @@
       <c r="K9" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=138.0.7204.184); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+  (Session info: chrome=139.0.7258.67); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff6f54ae415+77285]
-	GetHandleVerifier [0x0x7ff6f54ae470+77376]
-	(No symbol) [0x0x7ff6f5279a6a]
-	(No symbol) [0x0x7ff6f52d0406]
-	(No symbol) [0x0x7ff6f52d06bc]
-	(No symbol) [0x0x7ff6f5323ac7]
-	(No symbol) [0x0x7ff6f52f864f]
-	(No symbol) [0x0x7ff6f532087f]
-	(No symbol) [0x0x7ff6f52f83e3]
-	(No symbol) [0x0x7ff6f52c1521]
-	(No symbol) [0x0x7ff6f52c22b3]
-	GetHandleVerifier [0x0x7ff6f5791efd+3107021]
-	GetHandleVerifier [0x0x7ff6f578c29d+3083373]
-	GetHandleVerifier [0x0x7ff6f57abedd+3213485]
-	GetHandleVerifier [0x0x7ff6f54c884e+184862]
-	GetHandleVerifier [0x0x7ff6f54d055f+216879]
-	GetHandleVerifier [0x0x7ff6f54b7084+113236]
-	GetHandleVerifier [0x0x7ff6f54b7239+113673]
-	GetHandleVerifier [0x0x7ff6f549e298+11368]
+	GetHandleVerifier [0x0x7ff6fc6a6b55+79621]
+	GetHandleVerifier [0x0x7ff6fc6a6bb0+79712]
+	(No symbol) [0x0x7ff6fc43c0ea]
+	(No symbol) [0x0x7ff6fc492f56]
+	(No symbol) [0x0x7ff6fc49320c]
+	(No symbol) [0x0x7ff6fc4e65b7]
+	(No symbol) [0x0x7ff6fc4bb17f]
+	(No symbol) [0x0x7ff6fc4e33d0]
+	(No symbol) [0x0x7ff6fc4baf13]
+	(No symbol) [0x0x7ff6fc484151]
+	(No symbol) [0x0x7ff6fc484ee3]
+	GetHandleVerifier [0x0x7ff6fc96686d+2962461]
+	GetHandleVerifier [0x0x7ff6fc960b8d+2938685]
+	GetHandleVerifier [0x0x7ff6fc97f74d+3064573]
+	GetHandleVerifier [0x0x7ff6fc6c0c9e+186446]
+	GetHandleVerifier [0x0x7ff6fc6c8a6f+218655]
+	GetHandleVerifier [0x0x7ff6fc6af944+115956]
+	GetHandleVerifier [0x0x7ff6fc6afaf9+116393]
+	GetHandleVerifier [0x0x7ff6fc695f28+10968]
 	BaseThreadInitThunk [0x0x7ffde661e8d7+23]
 	RtlUserThreadStart [0x0x7ffde699c34c+44]
 </t>
@@ -1302,17 +1302,17 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>£28.82</t>
+          <t>£28.80</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>£28.82</t>
+          <t>£28.80</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>£28.82</t>
+          <t>£28.80</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -1343,27 +1343,27 @@
       <c r="K10" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=138.0.7204.184); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+  (Session info: chrome=139.0.7258.67); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff6f54ae415+77285]
-	GetHandleVerifier [0x0x7ff6f54ae470+77376]
-	(No symbol) [0x0x7ff6f5279a6a]
-	(No symbol) [0x0x7ff6f52d0406]
-	(No symbol) [0x0x7ff6f52d06bc]
-	(No symbol) [0x0x7ff6f5323ac7]
-	(No symbol) [0x0x7ff6f52f864f]
-	(No symbol) [0x0x7ff6f532087f]
-	(No symbol) [0x0x7ff6f52f83e3]
-	(No symbol) [0x0x7ff6f52c1521]
-	(No symbol) [0x0x7ff6f52c22b3]
-	GetHandleVerifier [0x0x7ff6f5791efd+3107021]
-	GetHandleVerifier [0x0x7ff6f578c29d+3083373]
-	GetHandleVerifier [0x0x7ff6f57abedd+3213485]
-	GetHandleVerifier [0x0x7ff6f54c884e+184862]
-	GetHandleVerifier [0x0x7ff6f54d055f+216879]
-	GetHandleVerifier [0x0x7ff6f54b7084+113236]
-	GetHandleVerifier [0x0x7ff6f54b7239+113673]
-	GetHandleVerifier [0x0x7ff6f549e298+11368]
+	GetHandleVerifier [0x0x7ff6fc6a6b55+79621]
+	GetHandleVerifier [0x0x7ff6fc6a6bb0+79712]
+	(No symbol) [0x0x7ff6fc43c0ea]
+	(No symbol) [0x0x7ff6fc492f56]
+	(No symbol) [0x0x7ff6fc49320c]
+	(No symbol) [0x0x7ff6fc4e65b7]
+	(No symbol) [0x0x7ff6fc4bb17f]
+	(No symbol) [0x0x7ff6fc4e33d0]
+	(No symbol) [0x0x7ff6fc4baf13]
+	(No symbol) [0x0x7ff6fc484151]
+	(No symbol) [0x0x7ff6fc484ee3]
+	GetHandleVerifier [0x0x7ff6fc96686d+2962461]
+	GetHandleVerifier [0x0x7ff6fc960b8d+2938685]
+	GetHandleVerifier [0x0x7ff6fc97f74d+3064573]
+	GetHandleVerifier [0x0x7ff6fc6c0c9e+186446]
+	GetHandleVerifier [0x0x7ff6fc6c8a6f+218655]
+	GetHandleVerifier [0x0x7ff6fc6af944+115956]
+	GetHandleVerifier [0x0x7ff6fc6afaf9+116393]
+	GetHandleVerifier [0x0x7ff6fc695f28+10968]
 	BaseThreadInitThunk [0x0x7ffde661e8d7+23]
 	RtlUserThreadStart [0x0x7ffde699c34c+44]
 </t>
@@ -1403,17 +1403,17 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>£28.50</t>
+          <t>£28.35</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>£28.50</t>
+          <t>£28.35</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>£28.50</t>
+          <t>£28.35</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1444,27 +1444,27 @@
       <c r="K11" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=138.0.7204.184); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+  (Session info: chrome=139.0.7258.67); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff6f54ae415+77285]
-	GetHandleVerifier [0x0x7ff6f54ae470+77376]
-	(No symbol) [0x0x7ff6f5279a6a]
-	(No symbol) [0x0x7ff6f52d0406]
-	(No symbol) [0x0x7ff6f52d06bc]
-	(No symbol) [0x0x7ff6f5323ac7]
-	(No symbol) [0x0x7ff6f52f864f]
-	(No symbol) [0x0x7ff6f532087f]
-	(No symbol) [0x0x7ff6f52f83e3]
-	(No symbol) [0x0x7ff6f52c1521]
-	(No symbol) [0x0x7ff6f52c22b3]
-	GetHandleVerifier [0x0x7ff6f5791efd+3107021]
-	GetHandleVerifier [0x0x7ff6f578c29d+3083373]
-	GetHandleVerifier [0x0x7ff6f57abedd+3213485]
-	GetHandleVerifier [0x0x7ff6f54c884e+184862]
-	GetHandleVerifier [0x0x7ff6f54d055f+216879]
-	GetHandleVerifier [0x0x7ff6f54b7084+113236]
-	GetHandleVerifier [0x0x7ff6f54b7239+113673]
-	GetHandleVerifier [0x0x7ff6f549e298+11368]
+	GetHandleVerifier [0x0x7ff6fc6a6b55+79621]
+	GetHandleVerifier [0x0x7ff6fc6a6bb0+79712]
+	(No symbol) [0x0x7ff6fc43c0ea]
+	(No symbol) [0x0x7ff6fc492f56]
+	(No symbol) [0x0x7ff6fc49320c]
+	(No symbol) [0x0x7ff6fc4e65b7]
+	(No symbol) [0x0x7ff6fc4bb17f]
+	(No symbol) [0x0x7ff6fc4e33d0]
+	(No symbol) [0x0x7ff6fc4baf13]
+	(No symbol) [0x0x7ff6fc484151]
+	(No symbol) [0x0x7ff6fc484ee3]
+	GetHandleVerifier [0x0x7ff6fc96686d+2962461]
+	GetHandleVerifier [0x0x7ff6fc960b8d+2938685]
+	GetHandleVerifier [0x0x7ff6fc97f74d+3064573]
+	GetHandleVerifier [0x0x7ff6fc6c0c9e+186446]
+	GetHandleVerifier [0x0x7ff6fc6c8a6f+218655]
+	GetHandleVerifier [0x0x7ff6fc6af944+115956]
+	GetHandleVerifier [0x0x7ff6fc6afaf9+116393]
+	GetHandleVerifier [0x0x7ff6fc695f28+10968]
 	BaseThreadInitThunk [0x0x7ffde661e8d7+23]
 	RtlUserThreadStart [0x0x7ffde699c34c+44]
 </t>
@@ -1545,27 +1545,27 @@
       <c r="K12" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=138.0.7204.184); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+  (Session info: chrome=139.0.7258.67); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff6f54ae415+77285]
-	GetHandleVerifier [0x0x7ff6f54ae470+77376]
-	(No symbol) [0x0x7ff6f5279a6a]
-	(No symbol) [0x0x7ff6f52d0406]
-	(No symbol) [0x0x7ff6f52d06bc]
-	(No symbol) [0x0x7ff6f5323ac7]
-	(No symbol) [0x0x7ff6f52f864f]
-	(No symbol) [0x0x7ff6f532087f]
-	(No symbol) [0x0x7ff6f52f83e3]
-	(No symbol) [0x0x7ff6f52c1521]
-	(No symbol) [0x0x7ff6f52c22b3]
-	GetHandleVerifier [0x0x7ff6f5791efd+3107021]
-	GetHandleVerifier [0x0x7ff6f578c29d+3083373]
-	GetHandleVerifier [0x0x7ff6f57abedd+3213485]
-	GetHandleVerifier [0x0x7ff6f54c884e+184862]
-	GetHandleVerifier [0x0x7ff6f54d055f+216879]
-	GetHandleVerifier [0x0x7ff6f54b7084+113236]
-	GetHandleVerifier [0x0x7ff6f54b7239+113673]
-	GetHandleVerifier [0x0x7ff6f549e298+11368]
+	GetHandleVerifier [0x0x7ff6fc6a6b55+79621]
+	GetHandleVerifier [0x0x7ff6fc6a6bb0+79712]
+	(No symbol) [0x0x7ff6fc43c0ea]
+	(No symbol) [0x0x7ff6fc492f56]
+	(No symbol) [0x0x7ff6fc49320c]
+	(No symbol) [0x0x7ff6fc4e65b7]
+	(No symbol) [0x0x7ff6fc4bb17f]
+	(No symbol) [0x0x7ff6fc4e33d0]
+	(No symbol) [0x0x7ff6fc4baf13]
+	(No symbol) [0x0x7ff6fc484151]
+	(No symbol) [0x0x7ff6fc484ee3]
+	GetHandleVerifier [0x0x7ff6fc96686d+2962461]
+	GetHandleVerifier [0x0x7ff6fc960b8d+2938685]
+	GetHandleVerifier [0x0x7ff6fc97f74d+3064573]
+	GetHandleVerifier [0x0x7ff6fc6c0c9e+186446]
+	GetHandleVerifier [0x0x7ff6fc6c8a6f+218655]
+	GetHandleVerifier [0x0x7ff6fc6af944+115956]
+	GetHandleVerifier [0x0x7ff6fc6afaf9+116393]
+	GetHandleVerifier [0x0x7ff6fc695f28+10968]
 	BaseThreadInitThunk [0x0x7ffde661e8d7+23]
 	RtlUserThreadStart [0x0x7ffde699c34c+44]
 </t>
@@ -1605,17 +1605,17 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>£34.99</t>
+          <t>£34.90</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>£34.99</t>
+          <t>£34.90</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>£34.99</t>
+          <t>£34.90</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1646,27 +1646,27 @@
       <c r="K13" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=138.0.7204.184); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+  (Session info: chrome=139.0.7258.67); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff6f54ae415+77285]
-	GetHandleVerifier [0x0x7ff6f54ae470+77376]
-	(No symbol) [0x0x7ff6f5279a6a]
-	(No symbol) [0x0x7ff6f52d0406]
-	(No symbol) [0x0x7ff6f52d06bc]
-	(No symbol) [0x0x7ff6f5323ac7]
-	(No symbol) [0x0x7ff6f52f864f]
-	(No symbol) [0x0x7ff6f532087f]
-	(No symbol) [0x0x7ff6f52f83e3]
-	(No symbol) [0x0x7ff6f52c1521]
-	(No symbol) [0x0x7ff6f52c22b3]
-	GetHandleVerifier [0x0x7ff6f5791efd+3107021]
-	GetHandleVerifier [0x0x7ff6f578c29d+3083373]
-	GetHandleVerifier [0x0x7ff6f57abedd+3213485]
-	GetHandleVerifier [0x0x7ff6f54c884e+184862]
-	GetHandleVerifier [0x0x7ff6f54d055f+216879]
-	GetHandleVerifier [0x0x7ff6f54b7084+113236]
-	GetHandleVerifier [0x0x7ff6f54b7239+113673]
-	GetHandleVerifier [0x0x7ff6f549e298+11368]
+	GetHandleVerifier [0x0x7ff6fc6a6b55+79621]
+	GetHandleVerifier [0x0x7ff6fc6a6bb0+79712]
+	(No symbol) [0x0x7ff6fc43c0ea]
+	(No symbol) [0x0x7ff6fc492f56]
+	(No symbol) [0x0x7ff6fc49320c]
+	(No symbol) [0x0x7ff6fc4e65b7]
+	(No symbol) [0x0x7ff6fc4bb17f]
+	(No symbol) [0x0x7ff6fc4e33d0]
+	(No symbol) [0x0x7ff6fc4baf13]
+	(No symbol) [0x0x7ff6fc484151]
+	(No symbol) [0x0x7ff6fc484ee3]
+	GetHandleVerifier [0x0x7ff6fc96686d+2962461]
+	GetHandleVerifier [0x0x7ff6fc960b8d+2938685]
+	GetHandleVerifier [0x0x7ff6fc97f74d+3064573]
+	GetHandleVerifier [0x0x7ff6fc6c0c9e+186446]
+	GetHandleVerifier [0x0x7ff6fc6c8a6f+218655]
+	GetHandleVerifier [0x0x7ff6fc6af944+115956]
+	GetHandleVerifier [0x0x7ff6fc6afaf9+116393]
+	GetHandleVerifier [0x0x7ff6fc695f28+10968]
 	BaseThreadInitThunk [0x0x7ffde661e8d7+23]
 	RtlUserThreadStart [0x0x7ffde699c34c+44]
 </t>
@@ -1824,27 +1824,27 @@
       <c r="K15" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=138.0.7204.184); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+  (Session info: chrome=139.0.7258.67); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff6f54ae415+77285]
-	GetHandleVerifier [0x0x7ff6f54ae470+77376]
-	(No symbol) [0x0x7ff6f5279a6a]
-	(No symbol) [0x0x7ff6f52d0406]
-	(No symbol) [0x0x7ff6f52d06bc]
-	(No symbol) [0x0x7ff6f5323ac7]
-	(No symbol) [0x0x7ff6f52f864f]
-	(No symbol) [0x0x7ff6f532087f]
-	(No symbol) [0x0x7ff6f52f83e3]
-	(No symbol) [0x0x7ff6f52c1521]
-	(No symbol) [0x0x7ff6f52c22b3]
-	GetHandleVerifier [0x0x7ff6f5791efd+3107021]
-	GetHandleVerifier [0x0x7ff6f578c29d+3083373]
-	GetHandleVerifier [0x0x7ff6f57abedd+3213485]
-	GetHandleVerifier [0x0x7ff6f54c884e+184862]
-	GetHandleVerifier [0x0x7ff6f54d055f+216879]
-	GetHandleVerifier [0x0x7ff6f54b7084+113236]
-	GetHandleVerifier [0x0x7ff6f54b7239+113673]
-	GetHandleVerifier [0x0x7ff6f549e298+11368]
+	GetHandleVerifier [0x0x7ff6fc6a6b55+79621]
+	GetHandleVerifier [0x0x7ff6fc6a6bb0+79712]
+	(No symbol) [0x0x7ff6fc43c0ea]
+	(No symbol) [0x0x7ff6fc492f56]
+	(No symbol) [0x0x7ff6fc49320c]
+	(No symbol) [0x0x7ff6fc4e65b7]
+	(No symbol) [0x0x7ff6fc4bb17f]
+	(No symbol) [0x0x7ff6fc4e33d0]
+	(No symbol) [0x0x7ff6fc4baf13]
+	(No symbol) [0x0x7ff6fc484151]
+	(No symbol) [0x0x7ff6fc484ee3]
+	GetHandleVerifier [0x0x7ff6fc96686d+2962461]
+	GetHandleVerifier [0x0x7ff6fc960b8d+2938685]
+	GetHandleVerifier [0x0x7ff6fc97f74d+3064573]
+	GetHandleVerifier [0x0x7ff6fc6c0c9e+186446]
+	GetHandleVerifier [0x0x7ff6fc6c8a6f+218655]
+	GetHandleVerifier [0x0x7ff6fc6af944+115956]
+	GetHandleVerifier [0x0x7ff6fc6afaf9+116393]
+	GetHandleVerifier [0x0x7ff6fc695f28+10968]
 	BaseThreadInitThunk [0x0x7ffde661e8d7+23]
 	RtlUserThreadStart [0x0x7ffde699c34c+44]
 </t>
@@ -1925,27 +1925,27 @@
       <c r="K16" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=138.0.7204.184); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+  (Session info: chrome=139.0.7258.67); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff6f54ae415+77285]
-	GetHandleVerifier [0x0x7ff6f54ae470+77376]
-	(No symbol) [0x0x7ff6f5279a6a]
-	(No symbol) [0x0x7ff6f52d0406]
-	(No symbol) [0x0x7ff6f52d06bc]
-	(No symbol) [0x0x7ff6f5323ac7]
-	(No symbol) [0x0x7ff6f52f864f]
-	(No symbol) [0x0x7ff6f532087f]
-	(No symbol) [0x0x7ff6f52f83e3]
-	(No symbol) [0x0x7ff6f52c1521]
-	(No symbol) [0x0x7ff6f52c22b3]
-	GetHandleVerifier [0x0x7ff6f5791efd+3107021]
-	GetHandleVerifier [0x0x7ff6f578c29d+3083373]
-	GetHandleVerifier [0x0x7ff6f57abedd+3213485]
-	GetHandleVerifier [0x0x7ff6f54c884e+184862]
-	GetHandleVerifier [0x0x7ff6f54d055f+216879]
-	GetHandleVerifier [0x0x7ff6f54b7084+113236]
-	GetHandleVerifier [0x0x7ff6f54b7239+113673]
-	GetHandleVerifier [0x0x7ff6f549e298+11368]
+	GetHandleVerifier [0x0x7ff6fc6a6b55+79621]
+	GetHandleVerifier [0x0x7ff6fc6a6bb0+79712]
+	(No symbol) [0x0x7ff6fc43c0ea]
+	(No symbol) [0x0x7ff6fc492f56]
+	(No symbol) [0x0x7ff6fc49320c]
+	(No symbol) [0x0x7ff6fc4e65b7]
+	(No symbol) [0x0x7ff6fc4bb17f]
+	(No symbol) [0x0x7ff6fc4e33d0]
+	(No symbol) [0x0x7ff6fc4baf13]
+	(No symbol) [0x0x7ff6fc484151]
+	(No symbol) [0x0x7ff6fc484ee3]
+	GetHandleVerifier [0x0x7ff6fc96686d+2962461]
+	GetHandleVerifier [0x0x7ff6fc960b8d+2938685]
+	GetHandleVerifier [0x0x7ff6fc97f74d+3064573]
+	GetHandleVerifier [0x0x7ff6fc6c0c9e+186446]
+	GetHandleVerifier [0x0x7ff6fc6c8a6f+218655]
+	GetHandleVerifier [0x0x7ff6fc6af944+115956]
+	GetHandleVerifier [0x0x7ff6fc6afaf9+116393]
+	GetHandleVerifier [0x0x7ff6fc695f28+10968]
 	BaseThreadInitThunk [0x0x7ffde661e8d7+23]
 	RtlUserThreadStart [0x0x7ffde699c34c+44]
 </t>
@@ -2026,27 +2026,27 @@
       <c r="K17" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=138.0.7204.184); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+  (Session info: chrome=139.0.7258.67); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff6f54ae415+77285]
-	GetHandleVerifier [0x0x7ff6f54ae470+77376]
-	(No symbol) [0x0x7ff6f5279a6a]
-	(No symbol) [0x0x7ff6f52d0406]
-	(No symbol) [0x0x7ff6f52d06bc]
-	(No symbol) [0x0x7ff6f5323ac7]
-	(No symbol) [0x0x7ff6f52f864f]
-	(No symbol) [0x0x7ff6f532087f]
-	(No symbol) [0x0x7ff6f52f83e3]
-	(No symbol) [0x0x7ff6f52c1521]
-	(No symbol) [0x0x7ff6f52c22b3]
-	GetHandleVerifier [0x0x7ff6f5791efd+3107021]
-	GetHandleVerifier [0x0x7ff6f578c29d+3083373]
-	GetHandleVerifier [0x0x7ff6f57abedd+3213485]
-	GetHandleVerifier [0x0x7ff6f54c884e+184862]
-	GetHandleVerifier [0x0x7ff6f54d055f+216879]
-	GetHandleVerifier [0x0x7ff6f54b7084+113236]
-	GetHandleVerifier [0x0x7ff6f54b7239+113673]
-	GetHandleVerifier [0x0x7ff6f549e298+11368]
+	GetHandleVerifier [0x0x7ff6fc6a6b55+79621]
+	GetHandleVerifier [0x0x7ff6fc6a6bb0+79712]
+	(No symbol) [0x0x7ff6fc43c0ea]
+	(No symbol) [0x0x7ff6fc492f56]
+	(No symbol) [0x0x7ff6fc49320c]
+	(No symbol) [0x0x7ff6fc4e65b7]
+	(No symbol) [0x0x7ff6fc4bb17f]
+	(No symbol) [0x0x7ff6fc4e33d0]
+	(No symbol) [0x0x7ff6fc4baf13]
+	(No symbol) [0x0x7ff6fc484151]
+	(No symbol) [0x0x7ff6fc484ee3]
+	GetHandleVerifier [0x0x7ff6fc96686d+2962461]
+	GetHandleVerifier [0x0x7ff6fc960b8d+2938685]
+	GetHandleVerifier [0x0x7ff6fc97f74d+3064573]
+	GetHandleVerifier [0x0x7ff6fc6c0c9e+186446]
+	GetHandleVerifier [0x0x7ff6fc6c8a6f+218655]
+	GetHandleVerifier [0x0x7ff6fc6af944+115956]
+	GetHandleVerifier [0x0x7ff6fc6afaf9+116393]
+	GetHandleVerifier [0x0x7ff6fc695f28+10968]
 	BaseThreadInitThunk [0x0x7ffde661e8d7+23]
 	RtlUserThreadStart [0x0x7ffde699c34c+44]
 </t>
